--- a/IMRADS/TALISAY/Distances/shel_work_distance_matrix.xlsx
+++ b/IMRADS/TALISAY/Distances/shel_work_distance_matrix.xlsx
@@ -1,49 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\TALISAY\Distances\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3478905E-BFD7-4A12-9315-6A83B026FD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>San Fernado Brgy. Hall</t>
-  </si>
-  <si>
-    <t>SantaClara Brgy. Hall</t>
-  </si>
-  <si>
-    <t>Darasa Brgy. Hall</t>
-  </si>
-  <si>
-    <t>San Antonio Brgy. Hall</t>
-  </si>
-  <si>
-    <t>Tagaytay Unida Church</t>
-  </si>
-  <si>
-    <t>Maugat Gymnasium</t>
-  </si>
-  <si>
-    <t>Brgy.San Jose BB Court</t>
-  </si>
-  <si>
-    <t>Suplang Covered Court</t>
-  </si>
-  <si>
-    <t>City EC of Sto. Tomas</t>
-  </si>
-  <si>
-    <t>Brgy. Asis-3 EC</t>
+    <t>PEDRO ALEGRE AURE SENIORHIGH SCHOOL</t>
+  </si>
+  <si>
+    <t>SILANG JUNCTION SOUTH</t>
+  </si>
+  <si>
+    <t>SUPLANG</t>
+  </si>
+  <si>
+    <t>LUYOS</t>
+  </si>
+  <si>
+    <t>DAYAPAN ELEMENTARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SAMBAT</t>
+  </si>
+  <si>
+    <t>TRAPICHE BASKETBALL COURT</t>
+  </si>
+  <si>
+    <t>TINURIK</t>
+  </si>
+  <si>
+    <t>POBLACION</t>
+  </si>
+  <si>
+    <t>SANTA CLARA</t>
   </si>
   <si>
     <t>Shelters</t>
@@ -55,8 +61,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,17 +114,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -165,7 +180,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -197,9 +212,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -231,6 +264,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -406,11 +457,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -445,39 +496,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
-        <v>15.517703</v>
-      </c>
-      <c r="C2">
-        <v>48.83243400000002</v>
-      </c>
-      <c r="D2">
-        <v>8.224478999999999</v>
-      </c>
-      <c r="E2">
-        <v>47.07188100000001</v>
-      </c>
-      <c r="F2">
-        <v>21.50715899999999</v>
-      </c>
-      <c r="G2">
-        <v>64.88919499999992</v>
-      </c>
-      <c r="H2">
-        <v>51.06430300000002</v>
-      </c>
-      <c r="I2">
-        <v>10.449426</v>
-      </c>
-      <c r="J2">
-        <v>3.669908</v>
-      </c>
-      <c r="K2">
-        <v>33.26482799999999</v>
+      <c r="B2" s="2">
+        <v>35.098802000000013</v>
+      </c>
+      <c r="C2" s="2">
+        <v>29.838674000000001</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10.601125</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9.6592199999999995</v>
+      </c>
+      <c r="F2" s="2">
+        <v>10.02792</v>
+      </c>
+      <c r="G2" s="2">
+        <v>8.8259579999999982</v>
+      </c>
+      <c r="H2" s="2">
+        <v>8.1426299999999987</v>
+      </c>
+      <c r="I2" s="2">
+        <v>10.798280999999999</v>
+      </c>
+      <c r="J2" s="2">
+        <v>12.093189000000001</v>
+      </c>
+      <c r="K2" s="2">
+        <v>16.519373000000002</v>
       </c>
     </row>
   </sheetData>
